--- a/Config/Luban/source/TbArena.xlsx
+++ b/Config/Luban/source/TbArena.xlsx
@@ -1,76 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arena" sheetId="1" r:id="R7fe84b87c3bd48ee"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arena" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="4">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE8EEF4"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF243E56"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="7">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+  </fonts>
+  <fills count="4">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF243E56"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -265,109 +332,178 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>sceneAddress</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>size</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>cellSize</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>layoutVersion</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="3" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" s="3" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="E2" s="3" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="F2" s="3" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="str">
-        <x:v>int</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="6" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="str">
-        <x:v>场地 ID</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="str">
-        <x:v>场地名称</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="str">
-        <x:v>场景地址</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="str">
-        <x:v>场地边长（米）</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="str">
-        <x:v>归属网格边长（米）</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="str">
-        <x:v>场地布局协议版本</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="2" t="str"/>
-      <x:c r="B4" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="str">
-        <x:v>对称竞技场</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="str">
-        <x:v>Prototype/Arena</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="n">
-        <x:v>0.125</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>sceneAddress</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>cellSize</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>layoutVersion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>场地 ID</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>场地名称</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>场景地址</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>场地宽度 X（米）</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>场地长度 Z（米）</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>归属网格边长（米）</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>场地布局协议版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str"/>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>立体训练场</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>maps/TrainingGround</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Config/Luban/source/TbArena.xlsx
+++ b/Config/Luban/source/TbArena.xlsx
@@ -500,7 +500,7 @@
         <v>0.125</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
